--- a/assets/templates/teklif_sablonu.xlsx
+++ b/assets/templates/teklif_sablonu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus.DESKTOP-9F6EQVL\Desktop\teklif-hazirlama\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{180C0A6D-8465-4845-B3DD-B47C12C3A107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BCD755-93D0-491E-A1F8-A584E857943E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -192,9 +192,6 @@
     <t>Teklif çevresel testlerin bünyenizde ve bedelsiz olarak yapılacağı varsayılarak hazırlanmıştır.</t>
   </si>
   <si>
-    <t>Genel hüküm ve şartlar "https://antsiselektronik.com.tr/wp-content/uploads/2024/12/" adresinden indirilebilir.</t>
-  </si>
-  <si>
     <t>Ürünlerin faturası, ürünlerin sevkiyatına mütakip kesilecektir.</t>
   </si>
   <si>
@@ -208,6 +205,9 @@
   </si>
   <si>
     <t>Ankara / TÜRKİYE</t>
+  </si>
+  <si>
+    <t>Genel hüküm ve şartlar https://antsiselektronik.com.tr/wp-content/uploads/2024/12/General-Commercial-Terms-and-Conditions.pdf adresinden indirilebilir.</t>
   </si>
 </sst>
 </file>
@@ -625,11 +625,29 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -644,24 +662,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -763,7 +763,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1285729</xdr:colOff>
+      <xdr:colOff>1276204</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
@@ -1197,14 +1197,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="6" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="68"/>
-      <c r="B1" s="60"/>
-      <c r="C1" s="58" t="s">
+      <c r="A1" s="76"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="60"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="68"/>
       <c r="G1" s="51" t="s">
         <v>1</v>
       </c>
@@ -1214,12 +1214,12 @@
       <c r="I1" s="7"/>
     </row>
     <row r="2" spans="1:12" s="6" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="61"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="63"/>
+      <c r="A2" s="69"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="71"/>
       <c r="G2" s="8" t="s">
         <v>3</v>
       </c>
@@ -1228,12 +1228,12 @@
       </c>
     </row>
     <row r="3" spans="1:12" s="6" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="61"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="63"/>
+      <c r="A3" s="69"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="71"/>
       <c r="G3" s="8" t="s">
         <v>4</v>
       </c>
@@ -1242,12 +1242,12 @@
       </c>
     </row>
     <row r="4" spans="1:12" s="6" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="61"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="63"/>
+      <c r="A4" s="69"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="71"/>
       <c r="G4" s="8" t="s">
         <v>6</v>
       </c>
@@ -1257,12 +1257,12 @@
       <c r="L4" s="9"/>
     </row>
     <row r="5" spans="1:12" s="6" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="61"/>
-      <c r="B5" s="63"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="66"/>
+      <c r="A5" s="69"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="74"/>
       <c r="G5" s="10" t="s">
         <v>7</v>
       </c>
@@ -1272,9 +1272,9 @@
       <c r="L5" s="9"/>
     </row>
     <row r="6" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="67"/>
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
+      <c r="A6" s="75"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
       <c r="D6" s="11"/>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
@@ -1285,11 +1285,11 @@
       <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="73" t="s">
+      <c r="A7" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="72"/>
-      <c r="C7" s="72"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -1330,10 +1330,10 @@
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
-      <c r="F10" s="74" t="s">
+      <c r="F10" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="72"/>
+      <c r="G10" s="59"/>
       <c r="H10" s="22"/>
       <c r="I10" s="3"/>
     </row>
@@ -1353,11 +1353,11 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="71" t="s">
+      <c r="A12" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="72"/>
-      <c r="C12" s="72"/>
+      <c r="B12" s="59"/>
+      <c r="C12" s="59"/>
       <c r="D12" s="23"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
@@ -1386,8 +1386,8 @@
       <c r="H14" s="17"/>
     </row>
     <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="71"/>
-      <c r="B15" s="72"/>
+      <c r="A15" s="58"/>
+      <c r="B15" s="59"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
@@ -1432,10 +1432,10 @@
       <c r="H18" s="17"/>
     </row>
     <row r="19" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="76" t="s">
+      <c r="A19" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="72"/>
+      <c r="B19" s="59"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
@@ -1467,41 +1467,41 @@
       <c r="A22" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="70" t="s">
+      <c r="B22" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="56"/>
-      <c r="D22" s="57"/>
+      <c r="C22" s="63"/>
+      <c r="D22" s="56"/>
       <c r="E22" s="29" t="s">
         <v>27</v>
       </c>
       <c r="F22" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G22" s="70" t="s">
+      <c r="G22" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="H22" s="57"/>
+      <c r="H22" s="56"/>
     </row>
     <row r="23" spans="1:8" s="4" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="75" t="s">
+      <c r="B23" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="56"/>
-      <c r="D23" s="57"/>
+      <c r="C23" s="63"/>
+      <c r="D23" s="56"/>
       <c r="E23" s="31" t="s">
         <v>32</v>
       </c>
       <c r="F23" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="69" t="s">
+      <c r="G23" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="H23" s="57"/>
+      <c r="H23" s="56"/>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="46"/>
@@ -1530,12 +1530,12 @@
       <c r="B26" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="70" t="s">
+      <c r="C26" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="57"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="63"/>
+      <c r="F26" s="56"/>
       <c r="G26" s="29" t="s">
         <v>38</v>
       </c>
@@ -1546,10 +1546,10 @@
     <row r="27" spans="1:8" s="4" customFormat="1" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="34"/>
       <c r="B27" s="30"/>
-      <c r="C27" s="55"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="56"/>
-      <c r="F27" s="57"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="63"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="56"/>
       <c r="G27" s="35">
         <v>0</v>
       </c>
@@ -1561,10 +1561,10 @@
     <row r="28" spans="1:8" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="34"/>
       <c r="B28" s="30"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="57"/>
+      <c r="C28" s="65"/>
+      <c r="D28" s="63"/>
+      <c r="E28" s="63"/>
+      <c r="F28" s="56"/>
       <c r="G28" s="35">
         <v>0</v>
       </c>
@@ -1728,7 +1728,7 @@
     </row>
     <row r="41" spans="1:9" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="18" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -1740,7 +1740,7 @@
     </row>
     <row r="42" spans="1:9" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -1785,6 +1785,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C1:F5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="A1:B5"/>
+    <mergeCell ref="C26:F26"/>
     <mergeCell ref="G23:H23"/>
     <mergeCell ref="G22:H22"/>
     <mergeCell ref="A12:C12"/>
@@ -1794,12 +1800,6 @@
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C1:F5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="A1:B5"/>
-    <mergeCell ref="C26:F26"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.51181102362204722" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -1815,25 +1815,25 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="1"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="77" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="78"/>
     </row>
